--- a/data/packs/pack-template.xlsx
+++ b/data/packs/pack-template.xlsx
@@ -427,14 +427,14 @@
     <row r="3" ht="15" customHeight="1" s="7">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Account: &lt;ACC-NNNN&gt;</t>
+          <t>Account: &lt;ACCOUNT-NNNN&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="7">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Prepared by: P-LUC</t>
+          <t>Prepared by: Lucia Ferreira</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="4" ht="15" customHeight="1" s="7">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ESC-0409</t>
+          <t>ESCALATION-0409</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">

--- a/data/packs/pack-template.xlsx
+++ b/data/packs/pack-template.xlsx
@@ -479,7 +479,7 @@
     <row r="10" ht="15" customHeight="1" s="7">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Proposals created</t>
+          <t>Suggestions created</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -487,7 +487,7 @@
     <row r="11" ht="15" customHeight="1" s="7">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Deflected</t>
+          <t>Self-served</t>
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
@@ -534,7 +534,7 @@
     <row r="15" ht="15" customHeight="1" s="7">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Deflection rate</t>
+          <t>Self-service rate</t>
         </is>
       </c>
       <c r="B15" s="10">
@@ -565,7 +565,7 @@
     <row r="19" ht="15" customHeight="1" s="7">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Deflection, prior</t>
+          <t>Self-service, prior</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
